--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488178_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488178_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.4389</v>
+        <v>8.8887</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6035</v>
+        <v>6.4624</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8354</v>
+        <v>2.4263</v>
       </c>
       <c r="G2" t="n">
         <v>8.6683</v>
@@ -610,13 +610,13 @@
         <v>2.0382</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5449000000000001</v>
+        <v>-0.0951</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.092</v>
+        <v>-0.2331</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4529</v>
+        <v>0.138</v>
       </c>
       <c r="V2" t="n">
         <v>0.3155</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.2621</v>
+        <v>5.9911</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7136</v>
+        <v>3.0828</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5484</v>
+        <v>2.9083</v>
       </c>
       <c r="G3" t="n">
         <v>2.9278</v>
@@ -688,13 +688,13 @@
         <v>1.6676</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1871</v>
+        <v>0.9162</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6703</v>
+        <v>0.0395</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5168</v>
+        <v>0.8767</v>
       </c>
       <c r="V3" t="n">
         <v>2.5177</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2926</v>
+        <v>3.6898</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7337</v>
+        <v>2.1801</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5589</v>
+        <v>1.5097</v>
       </c>
       <c r="G4" t="n">
         <v>4.9212</v>
@@ -766,13 +766,13 @@
         <v>0.9264</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0592</v>
+        <v>0.4564</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5471</v>
+        <v>-0.1007</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6063</v>
+        <v>0.5571</v>
       </c>
       <c r="V4" t="n">
         <v>2.2033</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7863</v>
+        <v>3.3805</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3812</v>
+        <v>1.8277</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4051</v>
+        <v>1.5529</v>
       </c>
       <c r="G5" t="n">
         <v>4.3559</v>
@@ -844,13 +844,13 @@
         <v>1.8529</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1254</v>
+        <v>0.4688</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6566</v>
+        <v>-0.2101</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5312</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2589</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. TOURE</t>
+          <t>A. GALLEGO GÓMEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1541</v>
+        <v>1.8883</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.163</v>
+        <v>1.8883</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3171</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0706</v>
+        <v>1.8883</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.358</v>
+        <v>0.6441</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4287</v>
+        <v>1.2441</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2675</v>
+        <v>1.8883</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1845</v>
+        <v>0.6441</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0829</v>
+        <v>1.2441</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1968</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5426</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3457</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0279</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1816</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8463000000000001</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GALLEGO GÓMEZ</t>
+          <t>A. TOURE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8883</v>
+        <v>1.5649</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8883</v>
+        <v>-0.4568</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2.0216</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8883</v>
+        <v>0.0706</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6441</v>
+        <v>-0.358</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2441</v>
+        <v>0.4287</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8883</v>
+        <v>0.2675</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6441</v>
+        <v>0.1845</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2441</v>
+        <v>0.0829</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-0.1968</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.5426</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.3457</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.6676</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.4386</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.1122</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8099</v>
+        <v>1.3751</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2431</v>
+        <v>0.439</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5668</v>
+        <v>0.9361</v>
       </c>
       <c r="G8" t="n">
         <v>1.9682</v>
@@ -1078,13 +1078,13 @@
         <v>0.3706</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2885</v>
+        <v>0.2767</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3283</v>
+        <v>-0.1324</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0398</v>
+        <v>0.4091</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3139</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0795</v>
+        <v>0.4649</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3652</v>
+        <v>-1.8209</v>
       </c>
       <c r="F9" t="n">
         <v>2.2857</v>
@@ -1156,10 +1156,10 @@
         <v>2.2234</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2363</v>
+        <v>0.3081</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7996</v>
+        <v>-0.2552</v>
       </c>
       <c r="U9" t="n">
         <v>0.5633</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2677</v>
+        <v>-0.2431</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2677</v>
+        <v>-0.2431</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2841</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.6417</v>
       </c>
       <c r="E11" t="n">
         <v>-0.6102</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.0315</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7997</v>
@@ -1312,13 +1312,13 @@
         <v>0.1853</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0766</v>
+        <v>-0.0274</v>
       </c>
       <c r="T11" t="n">
         <v>0.0211</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0977</v>
+        <v>-0.0485</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.7040999999999999</v>
+        <v>-1.2917</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8283</v>
+        <v>-3.4158</v>
       </c>
       <c r="F12" t="n">
         <v>2.1242</v>
@@ -1390,10 +1390,10 @@
         <v>1.1117</v>
       </c>
       <c r="S12" t="n">
-        <v>1.0694</v>
+        <v>0.4819</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.171</v>
       </c>
       <c r="U12" t="n">
         <v>0.3109</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.7581</v>
+        <v>-3.6613</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.8517</v>
+        <v>-4.5579</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0936</v>
+        <v>0.8966</v>
       </c>
       <c r="G13" t="n">
         <v>0.5553</v>
@@ -1468,13 +1468,13 @@
         <v>0.9264</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3188</v>
+        <v>0.4156</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.383</v>
+        <v>-0.0892</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7018</v>
+        <v>0.5049</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>21.1318</v>
+        <v>21.4055</v>
       </c>
       <c r="E14" t="n">
-        <v>4.744999999999998</v>
+        <v>5.018699999999999</v>
       </c>
       <c r="F14" t="n">
         <v>16.3868</v>
@@ -1546,13 +1546,13 @@
         <v>12.9701</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4071</v>
+        <v>3.6808</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.175</v>
+        <v>-0.9013</v>
       </c>
       <c r="U14" t="n">
-        <v>4.582199999999999</v>
+        <v>4.5823</v>
       </c>
       <c r="V14" t="n">
         <v>5.037500000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9925</v>
+        <v>4.0302</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4404</v>
+        <v>0.2451</v>
       </c>
       <c r="F15" t="n">
-        <v>3.4329</v>
+        <v>3.7851</v>
       </c>
       <c r="G15" t="n">
         <v>1.4421</v>
@@ -1624,13 +1624,13 @@
         <v>3.7057</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2289</v>
+        <v>-0.1912</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1826</v>
+        <v>-0.4971</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0463</v>
+        <v>0.3059</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6244</v>
+        <v>1.8999</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7123</v>
+        <v>-0.2226</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3367</v>
+        <v>2.1226</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2612</v>
@@ -1702,13 +1702,13 @@
         <v>4.0763</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0234</v>
+        <v>0.2521</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9674</v>
+        <v>-0.4778</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.7299</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3144</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. LAGHRIDAT</t>
+          <t>M. ORTEGA CARO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0699</v>
+        <v>0.2651</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0046</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9346</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6124000000000001</v>
+        <v>-2.0914</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5118</v>
+        <v>-1.3724</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1242</v>
+        <v>-0.719</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5743</v>
+        <v>0.3096</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4084</v>
+        <v>-0.4381</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1659</v>
+        <v>0.7477</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1867</v>
+        <v>-2.401</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8966</v>
+        <v>-0.9343</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2901</v>
+        <v>-1.4667</v>
       </c>
       <c r="P17" t="n">
-        <v>2.0382</v>
+        <v>3.1499</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0382</v>
+        <v>3.1499</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9031</v>
+        <v>-0.7934</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4303</v>
+        <v>-1.0309</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4728</v>
+        <v>0.2375</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. ORTEGA CARO</t>
+          <t>S. LAGHRIDAT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6019</v>
+        <v>0.0397</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.113</v>
+        <v>1.3191</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5111</v>
+        <v>-1.2793</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.0914</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.3724</v>
+        <v>0.5118</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.719</v>
+        <v>-1.1242</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3096</v>
+        <v>1.5743</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4381</v>
+        <v>1.4084</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7477</v>
+        <v>0.1659</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.401</v>
+        <v>-2.1867</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9343</v>
+        <v>-0.8966</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4667</v>
+        <v>-1.2901</v>
       </c>
       <c r="P18" t="n">
-        <v>3.1499</v>
+        <v>2.0382</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.1499</v>
+        <v>2.0382</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6604</v>
+        <v>-0.1271</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.4226</v>
+        <v>-0.2552</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2378</v>
+        <v>0.1281</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.035</v>
+        <v>-0.7905</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8468</v>
+        <v>-0.553</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1882</v>
+        <v>-0.2375</v>
       </c>
       <c r="G19" t="n">
         <v>-0.3933</v>
@@ -1936,13 +1936,13 @@
         <v>1.297</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3823</v>
+        <v>-0.1377</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3619</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0204</v>
+        <v>-0.0696</v>
       </c>
       <c r="V19" t="n">
         <v>-0.63</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.985</v>
+        <v>-2.8818</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.626</v>
+        <v>-1.8011</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.359</v>
+        <v>-1.0807</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1158</v>
@@ -2014,13 +2014,13 @@
         <v>3.5205</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9292</v>
+        <v>0.0324</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8817</v>
+        <v>-0.2934</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0475</v>
+        <v>0.3258</v>
       </c>
       <c r="V20" t="n">
         <v>0.3133</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9469</v>
+        <v>-2.9222</v>
       </c>
       <c r="E21" t="n">
         <v>-0.5614</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3854</v>
+        <v>-2.3608</v>
       </c>
       <c r="G21" t="n">
         <v>-1.355</v>
@@ -2092,13 +2092,13 @@
         <v>0.1853</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5183</v>
+        <v>-0.4937</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2736</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2447</v>
+        <v>-0.2201</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2589</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. CAMPOS CAMPOS</t>
+          <t>T. LUCERO BARBEITO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1928</v>
+        <v>-3.1087</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3753</v>
+        <v>-2.6293</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8175</v>
+        <v>-0.4793</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5119</v>
+        <v>-2.678</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9175</v>
+        <v>-0.1236</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5944</v>
+        <v>-2.5544</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.23</v>
+        <v>-0.4913</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6186</v>
+        <v>0.773</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-1.2643</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2818</v>
+        <v>-2.1867</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2989</v>
+        <v>-0.8966</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.983</v>
+        <v>-1.2901</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.9264</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3706</v>
+        <v>1.8529</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1251</v>
+        <v>-0.7271</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2189</v>
+        <v>-0.5816</v>
       </c>
       <c r="U22" t="n">
-        <v>0.09379999999999999</v>
+        <v>-0.1455</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. LUCERO BARBEITO</t>
+          <t>J. CAMPOS CAMPOS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5502</v>
+        <v>-3.2667</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9231</v>
+        <v>-2.3753</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6271</v>
+        <v>-0.8914</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.678</v>
+        <v>-2.5119</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1236</v>
+        <v>-0.9175</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.5544</v>
+        <v>-1.5944</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4913</v>
+        <v>-1.23</v>
       </c>
       <c r="K23" t="n">
-        <v>0.773</v>
+        <v>-0.6186</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2643</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.1867</v>
+        <v>-1.2818</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8966</v>
+        <v>-0.2989</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2901</v>
+        <v>-0.983</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9264</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8529</v>
+        <v>0.3706</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1687</v>
+        <v>-0.199</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8754</v>
+        <v>-0.2189</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2932</v>
+        <v>0.0199</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.7295</v>
+        <v>-4.6556</v>
       </c>
       <c r="E24" t="n">
         <v>-1.9705</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.759</v>
+        <v>-2.6851</v>
       </c>
       <c r="G24" t="n">
         <v>-5.9626</v>
@@ -2326,13 +2326,13 @@
         <v>1.8529</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6198</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="T24" t="n">
         <v>-0.5508999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0689</v>
+        <v>0.005</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.7776</v>
+        <v>-9.0885</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.8226</v>
+        <v>-7.1163</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.955</v>
+        <v>-1.9722</v>
       </c>
       <c r="G25" t="n">
         <v>-8.1912</v>
@@ -2404,13 +2404,13 @@
         <v>2.9646</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4872</v>
+        <v>0.1763</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.041</v>
+        <v>-0.3348</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5282</v>
+        <v>0.5111</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2589</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-21.1321</v>
+        <v>-20.4791</v>
       </c>
       <c r="E26" t="n">
-        <v>-16.3868</v>
+        <v>-16.3866</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.745099999999999</v>
+        <v>-4.0922</v>
       </c>
       <c r="G26" t="n">
         <v>-24.7307</v>
@@ -2455,10 +2455,10 @@
         <v>-11.6736</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.718799999999999</v>
+        <v>-0.7187999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.829200000000001</v>
+        <v>-2.8292</v>
       </c>
       <c r="L26" t="n">
         <v>2.1105</v>
@@ -2482,13 +2482,13 @@
         <v>25.0139</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.4074</v>
+        <v>-2.7543</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.582300000000001</v>
+        <v>-4.5823</v>
       </c>
       <c r="U26" t="n">
-        <v>1.1751</v>
+        <v>1.828</v>
       </c>
       <c r="V26" t="n">
         <v>-5.0378</v>
